--- a/0308/features_CN.xlsx
+++ b/0308/features_CN.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,76 +683,1782 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2xg2-1.JPG</t>
+          <t>11.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>#F070C0/#78D8F0/#080808</t>
+          <t>#888880/#885060/#503040/#205820/#584868/#584058/#905068/#481820/#383028</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>亮粉紅色 (Hot Pink)/天藍色 (Sky Blue)/黑色 (Black)</t>
+          <t>灰色 (Gray)/暗灰色 (Dim Gray)/暗灰色 (Dim Gray)/森林綠 (Forest Green)/暗灰色 (Dim Gray)/暗灰色 (Dim Gray)/暗灰色 (Dim Gray)/栗色/酒紅 (Maroon)/黑色 (Black)</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>star: 6, person: 2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>star1: 0.022, star2: 0.024, star3: 0.023, star4: 0.022, star5: 0.020, star6: 0.021, person1: 0.125, person2: 0.742</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>star1: 0.007, star2: 0.007, star3: 0.007, star4: 0.007, star5: 0.006, star6: 0.006, person1: 0.039, person2: 0.228</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
         <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>house: 1, sun: 1, person: 5, cloud: 2</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>house1: 0.277, sun1: 0.107, person1: 0.200, cloud1: 0.128, person2: 0.083, cloud2: 0.081, person3: 0.044, person4: 0.064, person5: 0.018</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>house1: 0.074, sun1: 0.028, person1: 0.053, cloud1: 0.034, person2: 0.022, cloud2: 0.022, person3: 0.012, person4: 0.017, person5: 0.005</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>10</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12.JPG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#888880</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>灰色 (Gray)</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A1/B1/C1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>cloud: 2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>cloud1: 0.525, cloud2: 0.475</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>cloud1: 0.067, cloud2: 0.061</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14.jpg</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#B8B088/#908878/#988880</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>實木棕 (Burly Wood)/灰色 (Gray)/灰色 (Gray)</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>house: 1, cloud: 1, tree: 1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>house1: 0.539, cloud1: 0.016, tree1: 0.445</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>house1: 0.333, cloud1: 0.010, tree1: 0.275</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1pg06.JPG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#68D8F8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>天藍色 (Sky Blue)</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>house: 4, sun: 1, person: 1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>house1: 0.150, house2: 0.240, sun1: 0.026, house3: 0.109, house4: 0.139, person1: 0.337</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>house1: 0.118, house2: 0.188, sun1: 0.020, house3: 0.085, house4: 0.109, person1: 0.264</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1pg09-1.JPG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#D07080</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>A2/A3/B2/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>cloud: 2, sun: 1, person: 3, house: 1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>cloud1: 0.074, sun1: 0.041, person1: 0.056, person2: 0.110, person3: 0.052, house1: 0.640, cloud2: 0.025</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>cloud1: 0.018, sun1: 0.010, person1: 0.014, person2: 0.027, person3: 0.013, house1: 0.159, cloud2: 0.006</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1pg09-2.JPG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#D06880</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A1/A2/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>cloud: 2, person: 1, house: 2, sun: 1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>cloud1: 0.052, cloud2: 0.016, person1: 0.042, house1: 0.347, sun1: 0.032, house2: 0.510</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>cloud1: 0.017, cloud2: 0.006, person1: 0.014, house1: 0.116, sun1: 0.011, house2: 0.170</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1pg13-1.JPG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#D85068/#6068C0/#0858A0/#1888C8/#282838</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)/鋼青色 (Steel Blue)/藍綠/水鴨色 (Teal)/鋼青色 (Steel Blue)/黑色 (Black)</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>person: 2, house: 2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>person1: 0.030, person2: 0.018, house1: 0.565, house2: 0.387</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>person1: 0.009, person2: 0.006, house1: 0.178, house2: 0.122</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1pg14-2.JPG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#D85868/#F060B0/#80C868/#207050/#3068D8/#1880D8/#50D0F0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)/亮粉紅色 (Hot Pink)/淺綠色 (Light Green)/森林綠 (Forest Green)/寶石藍 (Royal Blue)/道奇藍 (Dodger Blue)/綠松石色 (Turquoise)</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>house: 1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>house1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>house1: 0.223</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1xg1-2.JPG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#D85068/#5080E0/#E870C8/#B8E0A0/#A8B8C0/#989090/#E0C0A0/#908078/#A0A0D8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)/寶石藍 (Royal Blue)/亮粉紅色 (Hot Pink)/淺綠色 (Light Green)/銀色 (Silver)/灰色 (Gray)/實木棕 (Burly Wood)/灰色 (Gray)/銀色 (Silver)</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>grass: 1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>grass1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>grass1: 0.003</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2.jpg</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#686868/#000000/#B0B0B0/#888888</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>暗灰色 (Dim Gray)/黑色 (Black)/銀色 (Silver)/灰色 (Gray)</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2xg1.JPG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#D88098/#101010</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)/黑色 (Black)</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>A1/A2/B1/B2/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>sun: 1, person: 1, tree: 1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>sun1: 0.153, person1: 0.306, tree1: 0.540</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>sun1: 0.040, person1: 0.080, tree1: 0.142</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2xg2-1.JPG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#F070C0/#78D8F0/#080808</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>亮粉紅色 (Hot Pink)/天藍色 (Sky Blue)/黑色 (Black)</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>house: 1, sun: 1, person: 5, cloud: 2</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>house1: 0.277, sun1: 0.107, person1: 0.200, cloud1: 0.128, person2: 0.083, cloud2: 0.081, person3: 0.044, person4: 0.064, person5: 0.018</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>house1: 0.074, sun1: 0.028, person1: 0.053, cloud1: 0.034, person2: 0.022, cloud2: 0.022, person3: 0.012, person4: 0.017, person5: 0.005</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2xg2-2.JPG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>#F070C0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>亮粉紅色 (Hot Pink)</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>B1/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>star: 1, house: 1, person: 2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>star1: 0.038, house1: 0.496, person1: 0.287, person2: 0.179</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>star1: 0.004, house1: 0.047, person1: 0.027, person2: 0.017</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2xg3.JPG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>#68C070/#D068A0/#E0A0D0/#686860/#38C8E0/#C87860</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>海藍綠 (Medium Sea Green)/亮粉紅色 (Hot Pink)/梅紅色 (Plum)/暗灰色 (Dim Gray)/綠松石色 (Turquoise)/秘魯色 (Peru)</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B2</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>grass: 1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>grass1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>grass1: 0.897</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2xg4.JPG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>#D07888/#E898E0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>鮭魚紅 (Salmon)/梅紅色 (Plum)</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>star: 1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>star1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>star1: 0.003</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2xg5.JPG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>#C0E0A8/#D02838/#785858/#D06098/#107850/#1070C0/#383880/#D8B058</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>銀色 (Silver)/猩紅色/緋紅 (Crimson)/暗灰色 (Dim Gray)/亮粉紅色 (Hot Pink)/藍綠/水鴨色 (Teal)/鋼青色 (Steel Blue)/靛色/深紫 (Indigo)/實木棕 (Burly Wood)</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>sun: 1, grass: 1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>sun1: 0.316, grass1: 0.684</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>sun1: 0.027, grass1: 0.059</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2xg6.JPG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>#4078E0/#30A8E0/#20A0D8/#E8E0B0/#F070C0/#0878C0/#807070/#80706F/#C03038/#183878/#385860</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>寶石藍 (Royal Blue)/道奇藍 (Dodger Blue)/道奇藍 (Dodger Blue)/蒼白金 (Pale Goldenrod)/亮粉紅色 (Hot Pink)/深青色 (Dark Cyan)/灰色 (Gray)/灰色 (Gray)/磚紅色 (Firebrick)/深藍/海軍藍 (Navy)/暗灰色 (Dim Gray)</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>A1/A2/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>flower: 1, person: 1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>flower1: 0.374, person1: 0.626</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>flower1: 0.005, person1: 0.008</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2xg7.JPG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>#E8A0F0/#50A848/#3068D0/#68B090/#D83840/#207850/#A88080/#7078C8/#B0D0F8/#88C870/#A8807F/#2888D0/#C8A0B0/#50B8E0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>梅紅色 (Plum)/海藍綠 (Medium Sea Green)/寶石藍 (Royal Blue)/海藍綠 (Medium Sea Green)/猩紅色/緋紅 (Crimson)/森林綠 (Forest Green)/灰色 (Gray)/鋼青色 (Steel Blue)/淺藍色 (Light Blue)/淺綠色 (Light Green)/灰色 (Gray)/鋼青色 (Steel Blue)/銀色 (Silver)/綠松石色 (Turquoise)</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>house: 1, flower: 1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>house1: 0.950, flower1: 0.050</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>house1: 0.506, flower1: 0.027</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2xg8.JPG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>#7078D8/#F070C0/#80C868/#D08090/#58B8E0/#58B048</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>矢車菊藍 (Cornflower Blue)/亮粉紅色 (Hot Pink)/淺綠色 (Light Green)/鮭魚紅 (Salmon)/綠松石色 (Turquoise)/海藍綠 (Medium Sea Green)</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>butterflies: 2, cloud: 3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>butterflies1: 0.075, cloud1: 0.337, cloud2: 0.439, cloud3: 0.084, butterflies2: 0.065</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>butterflies1: 0.009, cloud1: 0.040, cloud2: 0.052, cloud3: 0.010, butterflies2: 0.008</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>9</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2xg9.JPG</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>#E05090/#D02830/#48A078/#88D8F8/#98D8F8/#885098/#1080C0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>亮粉紅色 (Hot Pink)/猩紅色/緋紅 (Crimson)/海藍綠 (Medium Sea Green)/天藍色 (Sky Blue)/天藍色 (Sky Blue)/灰色 (Gray)/鋼青色 (Steel Blue)</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>A1/A2/B1/B2/C2/C3</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>flower: 1, person: 1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>flower1: 0.248, person1: 0.752</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>flower1: 0.032, person1: 0.098</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>a.jpg</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>#1840E8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>寶石藍 (Royal Blue)</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>A1/A2/B1/B2/B3</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>b.jpg</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>#1840E8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>寶石藍 (Royal Blue)</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C2/C3</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>star: 1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>star1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>star1: 0.031</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>c.jpg</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>#1040E0/#F0E810/#F8C840/#E03030</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>寶石藍 (Royal Blue)/金色 (Gold)/金色 (Gold)/猩紅色/緋紅 (Crimson)</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>star: 1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>star1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>star1: 0.030</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d.jpg</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>#B8C8F8/#F8E8A8/#9038E8/#F098F0/#E83838</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>淺藍色 (Light Blue)/蒼白金 (Pale Goldenrod)/藍紫色 (Blue Violet)/梅紅色 (Plum)/猩紅色/緋紅 (Crimson)</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>A1/A2/A3/B1/B2/B3/C1/C2/C3</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>star: 1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>star1: 1.000</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>star1: 0.031</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
